--- a/Production/TAbaseplate2/TA_Baseplate_V2.xlsx
+++ b/Production/TAbaseplate2/TA_Baseplate_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/TAbaseplate2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB474367-2E2A-DB40-AB81-6F662AD9BBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF75B11-6AAF-D843-B864-E828C3BDF6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="640" yWindow="740" windowWidth="14700" windowHeight="16680" xr2:uid="{4C8BA93B-15F4-BD4C-A123-DC586B369965}"/>
+    <workbookView xWindow="29400" yWindow="500" windowWidth="12800" windowHeight="21100" xr2:uid="{4C8BA93B-15F4-BD4C-A123-DC586B369965}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,10 +92,10 @@
     <t>IO-3D-780-VLP</t>
   </si>
   <si>
-    <t>circular_lens (f = 150 mm)</t>
-  </si>
-  <si>
     <t>BB05-E03</t>
+  </si>
+  <si>
+    <t>LA1614-B</t>
   </si>
 </sst>
 </file>
@@ -575,7 +575,7 @@
     </row>
     <row r="16" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
@@ -590,8 +590,8 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>18</v>
+      <c r="A18" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
@@ -647,6 +647,7 @@
     <hyperlink ref="A17" r:id="rId6" xr:uid="{25EECDFE-92ED-4D4C-B62B-77D92F9D3B2C}"/>
     <hyperlink ref="A15" r:id="rId7" xr:uid="{E5BDCA7F-2CF4-4949-9673-7DD790257BA1}"/>
     <hyperlink ref="A16" r:id="rId8" display="circular_mirror" xr:uid="{6B7189F7-A68F-AD4D-B6FE-981634C46653}"/>
+    <hyperlink ref="A18" r:id="rId9" xr:uid="{EF876521-849D-6D4B-9820-E2C0B7A206F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Production/TAbaseplate2/TA_Baseplate_V2.xlsx
+++ b/Production/TAbaseplate2/TA_Baseplate_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/TAbaseplate2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF75B11-6AAF-D843-B864-E828C3BDF6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988B187B-FE21-0F42-95DB-B501F4BF8601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="500" windowWidth="12800" windowHeight="21100" xr2:uid="{4C8BA93B-15F4-BD4C-A123-DC586B369965}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" xr2:uid="{4C8BA93B-15F4-BD4C-A123-DC586B369965}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>TA_Baseplate_V2</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>LA1614-B</t>
+  </si>
+  <si>
+    <t>TA_Baseplate2.step</t>
   </si>
 </sst>
 </file>
@@ -549,6 +552,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="13" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>14</v>

--- a/Production/TAbaseplate2/TA_Baseplate_V2.xlsx
+++ b/Production/TAbaseplate2/TA_Baseplate_V2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/TAbaseplate2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/josiahsinclair/Dropbox/2025-2032/SinclairLab/PyOpticL_Rubidium_System/Production/TAbaseplate2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988B187B-FE21-0F42-95DB-B501F4BF8601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C81E493-8010-FB4E-9F48-BED776EC2474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" xr2:uid="{4C8BA93B-15F4-BD4C-A123-DC586B369965}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16680" xr2:uid="{4C8BA93B-15F4-BD4C-A123-DC586B369965}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>TA_Baseplate_V2</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>TA_Baseplate2.step</t>
+  </si>
+  <si>
+    <t>Iris Adaptor</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE4F86D-9124-0842-A565-85DDB1A301A8}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
@@ -554,44 +557,44 @@
     </row>
     <row r="10" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1">
-        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1">
         <v>3</v>
@@ -599,23 +602,23 @@
     </row>
     <row r="18" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
@@ -623,15 +626,15 @@
     </row>
     <row r="21" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>10</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
@@ -639,23 +642,31 @@
     </row>
     <row r="23" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B24" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A13" r:id="rId1" xr:uid="{6E786827-FF2D-5346-88D3-375FCDA41C8E}"/>
-    <hyperlink ref="A14" r:id="rId2" xr:uid="{8390965A-7195-2A42-AF1B-5854895A15D5}"/>
-    <hyperlink ref="A19" r:id="rId3" xr:uid="{07E98017-A723-394F-B24E-732469DE3657}"/>
-    <hyperlink ref="A20" r:id="rId4" xr:uid="{B1B7AE46-E7C4-6844-9473-3E1D8717E3E2}"/>
-    <hyperlink ref="A21" r:id="rId5" xr:uid="{11E87089-7CA8-A24A-AFB4-A01880996CD6}"/>
-    <hyperlink ref="A17" r:id="rId6" xr:uid="{25EECDFE-92ED-4D4C-B62B-77D92F9D3B2C}"/>
-    <hyperlink ref="A15" r:id="rId7" xr:uid="{E5BDCA7F-2CF4-4949-9673-7DD790257BA1}"/>
-    <hyperlink ref="A16" r:id="rId8" display="circular_mirror" xr:uid="{6B7189F7-A68F-AD4D-B6FE-981634C46653}"/>
-    <hyperlink ref="A18" r:id="rId9" xr:uid="{EF876521-849D-6D4B-9820-E2C0B7A206F3}"/>
+    <hyperlink ref="A14" r:id="rId1" xr:uid="{6E786827-FF2D-5346-88D3-375FCDA41C8E}"/>
+    <hyperlink ref="A15" r:id="rId2" xr:uid="{8390965A-7195-2A42-AF1B-5854895A15D5}"/>
+    <hyperlink ref="A20" r:id="rId3" xr:uid="{07E98017-A723-394F-B24E-732469DE3657}"/>
+    <hyperlink ref="A21" r:id="rId4" xr:uid="{B1B7AE46-E7C4-6844-9473-3E1D8717E3E2}"/>
+    <hyperlink ref="A22" r:id="rId5" xr:uid="{11E87089-7CA8-A24A-AFB4-A01880996CD6}"/>
+    <hyperlink ref="A18" r:id="rId6" xr:uid="{25EECDFE-92ED-4D4C-B62B-77D92F9D3B2C}"/>
+    <hyperlink ref="A16" r:id="rId7" xr:uid="{E5BDCA7F-2CF4-4949-9673-7DD790257BA1}"/>
+    <hyperlink ref="A17" r:id="rId8" display="circular_mirror" xr:uid="{6B7189F7-A68F-AD4D-B6FE-981634C46653}"/>
+    <hyperlink ref="A19" r:id="rId9" xr:uid="{EF876521-849D-6D4B-9820-E2C0B7A206F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
